--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6204-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6204-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{935D95D1-F672-4D7F-8516-6BF806A87284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{99183D05-2AB8-4B82-828E-ADCDDE74748E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{A2C9FD22-64F6-4E64-9FA0-8E6EDE21A8D7}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{41F9262C-8562-4E94-BAEC-0FF46EA41877}"/>
   </bookViews>
   <sheets>
     <sheet name="6204-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1523,30 +1523,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D93E566-3A59-46A7-A618-8194C792FF48}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1AF73DE-1725-48EC-9D06-623BE1939973}">
   <dimension ref="A1:X37"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.75" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1580,7 +1580,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1616,7 +1616,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1736,7 +1736,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1808,7 +1808,7 @@
         <v>0.71</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2023</v>
       </c>
@@ -1880,7 +1880,7 @@
         <v>32.9</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
         <v>29</v>
       </c>
@@ -1954,7 +1954,7 @@
         <v>1.52</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
         <v>29</v>
       </c>
@@ -2028,7 +2028,7 @@
         <v>31.4</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2022</v>
       </c>
@@ -2100,7 +2100,7 @@
         <v>6.92</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>29</v>
       </c>
@@ -2174,7 +2174,7 @@
         <v>2.65</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>29</v>
       </c>
@@ -2248,7 +2248,7 @@
         <v>4.26</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="39">
         <v>2021</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>32.200000000000003</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
         <v>29</v>
       </c>
@@ -2394,7 +2394,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>29</v>
       </c>
@@ -2468,7 +2468,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="37">
         <v>2020</v>
       </c>
@@ -2540,7 +2540,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <v>2019</v>
       </c>
@@ -2612,7 +2612,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>2018</v>
       </c>
@@ -2684,7 +2684,7 @@
         <v>5.63</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="39">
         <v>2017</v>
       </c>
@@ -2756,7 +2756,7 @@
         <v>6.51</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2016</v>
       </c>
@@ -2828,7 +2828,7 @@
         <v>5.0599999999999996</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="39">
         <v>2015</v>
       </c>
@@ -2900,7 +2900,7 @@
         <v>3.61</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>2014</v>
       </c>
@@ -2972,7 +2972,7 @@
         <v>4.93</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="39">
         <v>2013</v>
       </c>
@@ -3044,7 +3044,7 @@
         <v>4.9800000000000004</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <v>2012</v>
       </c>
@@ -3116,7 +3116,7 @@
         <v>4.72</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="39">
         <v>2011</v>
       </c>
@@ -3188,7 +3188,7 @@
         <v>7.62</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2010</v>
       </c>
@@ -3260,7 +3260,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="39">
         <v>2009</v>
       </c>
@@ -3332,7 +3332,7 @@
         <v>7.68</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="37">
         <v>2008</v>
       </c>
@@ -3404,7 +3404,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="39">
         <v>2007</v>
       </c>
@@ -3476,7 +3476,7 @@
         <v>18.899999999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <v>2006</v>
       </c>
@@ -3548,7 +3548,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="39">
         <v>2005</v>
       </c>
@@ -3620,7 +3620,7 @@
         <v>8.32</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>2004</v>
       </c>
@@ -3692,7 +3692,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="39">
         <v>2003</v>
       </c>
@@ -3764,7 +3764,7 @@
         <v>8.0299999999999994</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="37">
         <v>2002</v>
       </c>
@@ -3836,7 +3836,7 @@
         <v>8.59</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="39">
         <v>2001</v>
       </c>
@@ -3908,7 +3908,7 @@
         <v>6.23</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="37">
         <v>2000</v>
       </c>
@@ -3980,7 +3980,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="39">
         <v>1999</v>
       </c>
@@ -4052,7 +4052,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="37" t="s">
         <v>60</v>
       </c>
